--- a/STEP2_ML/Step6_ML_Data_Preparation.xlsx
+++ b/STEP2_ML/Step6_ML_Data_Preparation.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-26 16:25:27</t>
+          <t>2026-10-02 20:34:09</t>
         </is>
       </c>
     </row>

--- a/STEP2_ML/Step6_ML_Data_Preparation.xlsx
+++ b/STEP2_ML/Step6_ML_Data_Preparation.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit_Results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ML_Train_297" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ML_Train_315" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ML_Holdout_17" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Train_Source_Provenance" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature_Statistics" sheetId="6" state="visible" r:id="rId6"/>
@@ -17,9 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target_Statistics_Holdout" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature_Correlation" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature_Target_Correlation" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scaling_Plan" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diameter_Coverage" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Distribution" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diameter_Coverage" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Distribution" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +459,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Step 6 — ML Data Preparation &amp; Leakage Audit</t>
+          <t>Step 6 - ML Data Preparation &amp; Leakage Audit</t>
         </is>
       </c>
     </row>
@@ -496,7 +495,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 18:21:34</t>
+          <t>2026-10-09 08:29:28</t>
         </is>
       </c>
     </row>
@@ -532,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Point_ID (sequential, not a feature)</t>
+          <t>Point_ID (sequential, not a model feature)</t>
         </is>
       </c>
     </row>
@@ -543,7 +542,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>297</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -554,7 +553,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ML_Train_297</t>
+          <t>ML_Train_315</t>
         </is>
       </c>
     </row>
@@ -595,7 +594,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -613,120 +612,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Leakage_Status</t>
+          <t>Provenance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>No coordinate overlap between train and holdout</t>
+          <t>measured + interpolated + extrapolated</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Physical_Status</t>
+          <t>Note_1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>All targets within physical bounds</t>
+          <t>Point_ID must never be passed to a model</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Provenance</t>
+          <t>Note_2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Training includes measured + interpolated points (extrapolation excluded)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Scaling_Policy</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>StandardScaler for SVR/KNN/MLP/GPR on features; not needed for trees</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Target_Transform_Policy</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>No target transformation by default (unless EDA justifies)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Rule_1</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Point_ID must NEVER be used as a model feature</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Rule_2</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ML_Holdout_17 must NEVER be used for model selection or tuning</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Rule_3</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Source provenance (MEASURED/INTERPOLATED/EXTRAPOLATED) tracked</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Rule_4</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>td_to is the correct column name (never td/to)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Rule_5</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Extrapolation points (RPM&gt;260) are reference-grade, clearly marked</t>
+          <t>ML_Holdout_17 is locked - not used for selection or tuning</t>
         </is>
       </c>
     </row>
@@ -768,13 +683,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.3295651426025153</v>
+        <v>-0.3107427257250159</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7710502333950302</v>
+        <v>0.7649812155751466</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3177867566654073</v>
+        <v>0.3423568859002736</v>
       </c>
     </row>
     <row r="3">
@@ -784,13 +699,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8599938074054102</v>
+        <v>0.7933273024187619</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4985347733726418</v>
+        <v>0.5126148342724778</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8527835538568089</v>
+        <v>0.7968131336029887</v>
       </c>
     </row>
   </sheetData>
@@ -804,198 +719,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>d</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>train_count</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Scale_For_SVR_KNN_MLP_GPR</t>
+          <t>holdout_count</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Scale_For_Tree_Models</t>
+          <t>total</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Target_Transform</t>
+          <t>train_RPM_min</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>train_RPM_max</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>holdout_RPMs</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>StandardScaler</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Not needed</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Port diameter [6-16 mm]</t>
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>53</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
+        <v>320</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>[0, 160, 240]</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Rpm</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>StandardScaler</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Not needed</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Rotational speed [0-260 RPM]</t>
+      <c r="A3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3" t="n">
+        <v>53</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>56</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>320</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>[40, 140, 260]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>hc_hi</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Not needed</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>No (unless EDA justifies)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Dimensionless, bounded [0,1]</t>
+      <c r="A4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B4" t="n">
+        <v>53</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>56</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>320</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>[0, 160, 200]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>td_to</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Not needed</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>No (unless EDA justifies)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Dimensionless, bounded [1, ~4.7]</t>
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>53</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>56</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>320</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>[0, 140, 260]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Vch</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Not needed</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>No (unless EDA justifies)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Dimensionless, bounded [0,1], zeros at RPM=0</t>
+      <c r="A6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B6" t="n">
+        <v>53</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>56</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>320</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>[60, 160, 240]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B7" t="n">
+        <v>53</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>55</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>320</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>[60, 140]</t>
         </is>
       </c>
     </row>
@@ -1010,213 +920,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>train_count</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>holdout_count</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>train_RPM_min</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>train_RPM_max</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>holdout_RPMs</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B2" t="n">
-        <v>47</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F2" t="n">
-        <v>260</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>[0, 160, 240]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B3" t="n">
-        <v>50</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>53</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>255</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>[40, 140, 260]</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="n">
-        <v>53</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>260</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>[0, 160, 200]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B5" t="n">
-        <v>50</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>53</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>255</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>[0, 140, 260]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B6" t="n">
-        <v>50</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>53</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>260</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>[60, 160, 240]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B7" t="n">
-        <v>50</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>52</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>260</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>[60, 140]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
           <t>Source</t>
         </is>
       </c>
@@ -1244,38 +953,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
+          <t>EXTRAPOLATED</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>280</v>
       </c>
       <c r="E2" t="n">
-        <v>255</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MEASURED</t>
+          <t>INTERPOLATED</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67</v>
+        <v>230</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>67</v>
+      </c>
+      <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>260</v>
       </c>
     </row>
@@ -1364,7 +1092,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Extrap_excluded</t>
+          <t>Extrap_physical_valid</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1374,7 +1102,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Extrapolation omitted from training</t>
+          <t>violations=0</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1119,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>297 rows (MEASURED=67, INTERPOLATED=230, EXTRAPOLATED=0)</t>
+          <t>315 rows (MEASURED=67, INTERPOLATED=230, EXTRAPOLATED=18)</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1323,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RPM range: 0 - 260</t>
+          <t>RPM range: 0 - 320</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F298"/>
+  <dimension ref="A1:F316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7685,6 +7413,366 @@
       </c>
       <c r="F298" t="n">
         <v>0.367215621</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="n">
+        <v>6</v>
+      </c>
+      <c r="C299" t="n">
+        <v>280</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0.9326496002842941</v>
+      </c>
+      <c r="E299" t="n">
+        <v>1.663745027696047</v>
+      </c>
+      <c r="F299" t="n">
+        <v>0.169052267517873</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="n">
+        <v>6</v>
+      </c>
+      <c r="C300" t="n">
+        <v>300</v>
+      </c>
+      <c r="D300" t="n">
+        <v>0.8998067434432557</v>
+      </c>
+      <c r="E300" t="n">
+        <v>1.734558166222635</v>
+      </c>
+      <c r="F300" t="n">
+        <v>0.1609235239474326</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="n">
+        <v>6</v>
+      </c>
+      <c r="C301" t="n">
+        <v>320</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0.8581662778111887</v>
+      </c>
+      <c r="E301" t="n">
+        <v>1.830263392895952</v>
+      </c>
+      <c r="F301" t="n">
+        <v>0.1501860007202795</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="n">
+        <v>8</v>
+      </c>
+      <c r="C302" t="n">
+        <v>280</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0.7516530556121941</v>
+      </c>
+      <c r="E302" t="n">
+        <v>2.472298567350263</v>
+      </c>
+      <c r="F302" t="n">
+        <v>0.2179320108099463</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="n">
+        <v>8</v>
+      </c>
+      <c r="C303" t="n">
+        <v>300</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0.6477340179509133</v>
+      </c>
+      <c r="E303" t="n">
+        <v>2.673245540493734</v>
+      </c>
+      <c r="F303" t="n">
+        <v>0.1953137371906394</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="n">
+        <v>8</v>
+      </c>
+      <c r="C304" t="n">
+        <v>320</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0.5243051160977052</v>
+      </c>
+      <c r="E304" t="n">
+        <v>2.942710366938433</v>
+      </c>
+      <c r="F304" t="n">
+        <v>0.1677276599696758</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="n">
+        <v>10</v>
+      </c>
+      <c r="C305" t="n">
+        <v>280</v>
+      </c>
+      <c r="D305" t="n">
+        <v>0.916368419819064</v>
+      </c>
+      <c r="E305" t="n">
+        <v>2.72592254331555</v>
+      </c>
+      <c r="F305" t="n">
+        <v>0.274716630638852</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="n">
+        <v>10</v>
+      </c>
+      <c r="C306" t="n">
+        <v>300</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0.8847546142177997</v>
+      </c>
+      <c r="E306" t="n">
+        <v>2.846240433733532</v>
+      </c>
+      <c r="F306" t="n">
+        <v>0.2642455624805454</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="n">
+        <v>10</v>
+      </c>
+      <c r="C307" t="n">
+        <v>320</v>
+      </c>
+      <c r="D307" t="n">
+        <v>0.842683015683252</v>
+      </c>
+      <c r="E307" t="n">
+        <v>3.011418496297377</v>
+      </c>
+      <c r="F307" t="n">
+        <v>0.2499936551787242</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="n">
+        <v>12</v>
+      </c>
+      <c r="C308" t="n">
+        <v>280</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0.820844575463388</v>
+      </c>
+      <c r="E308" t="n">
+        <v>3.383980568390685</v>
+      </c>
+      <c r="F308" t="n">
+        <v>0.2788855180313104</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="n">
+        <v>12</v>
+      </c>
+      <c r="C309" t="n">
+        <v>300</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0.769045385574883</v>
+      </c>
+      <c r="E309" t="n">
+        <v>3.533872741356585</v>
+      </c>
+      <c r="F309" t="n">
+        <v>0.2603304625709384</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="n">
+        <v>12</v>
+      </c>
+      <c r="C310" t="n">
+        <v>320</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0.7041195374144459</v>
+      </c>
+      <c r="E310" t="n">
+        <v>3.74162039861249</v>
+      </c>
+      <c r="F310" t="n">
+        <v>0.2367792980130189</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="n">
+        <v>14</v>
+      </c>
+      <c r="C311" t="n">
+        <v>280</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0.88674517759075</v>
+      </c>
+      <c r="E311" t="n">
+        <v>4.021247141475929</v>
+      </c>
+      <c r="F311" t="n">
+        <v>0.3305159125664396</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="n">
+        <v>14</v>
+      </c>
+      <c r="C312" t="n">
+        <v>300</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0.8562867093687121</v>
+      </c>
+      <c r="E312" t="n">
+        <v>4.27929441303854</v>
+      </c>
+      <c r="F312" t="n">
+        <v>0.322147644293129</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="n">
+        <v>14</v>
+      </c>
+      <c r="C313" t="n">
+        <v>320</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0.8139623718837093</v>
+      </c>
+      <c r="E313" t="n">
+        <v>4.634756562536802</v>
+      </c>
+      <c r="F313" t="n">
+        <v>0.3095180522735725</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="n">
+        <v>16</v>
+      </c>
+      <c r="C314" t="n">
+        <v>280</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0.9083547852474255</v>
+      </c>
+      <c r="E314" t="n">
+        <v>4.903224542967129</v>
+      </c>
+      <c r="F314" t="n">
+        <v>0.3601017946267884</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" t="n">
+        <v>16</v>
+      </c>
+      <c r="C315" t="n">
+        <v>300</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0.8961379532598739</v>
+      </c>
+      <c r="E315" t="n">
+        <v>5.234610678271663</v>
+      </c>
+      <c r="F315" t="n">
+        <v>0.3600028963890111</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" t="n">
+        <v>16</v>
+      </c>
+      <c r="C316" t="n">
+        <v>320</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0.8740074121030386</v>
+      </c>
+      <c r="E316" t="n">
+        <v>5.671841586375268</v>
+      </c>
+      <c r="F316" t="n">
+        <v>0.3564200150499289</v>
       </c>
     </row>
   </sheetData>
@@ -8084,7 +8172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D298"/>
+  <dimension ref="A1:D316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12858,6 +12946,294 @@
       <c r="D298" t="inlineStr">
         <is>
           <t>MEASURED</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="n">
+        <v>6</v>
+      </c>
+      <c r="C299" t="n">
+        <v>280</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="n">
+        <v>6</v>
+      </c>
+      <c r="C300" t="n">
+        <v>300</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="n">
+        <v>6</v>
+      </c>
+      <c r="C301" t="n">
+        <v>320</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="n">
+        <v>8</v>
+      </c>
+      <c r="C302" t="n">
+        <v>280</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="n">
+        <v>8</v>
+      </c>
+      <c r="C303" t="n">
+        <v>300</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="n">
+        <v>8</v>
+      </c>
+      <c r="C304" t="n">
+        <v>320</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="n">
+        <v>10</v>
+      </c>
+      <c r="C305" t="n">
+        <v>280</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="n">
+        <v>10</v>
+      </c>
+      <c r="C306" t="n">
+        <v>300</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="n">
+        <v>10</v>
+      </c>
+      <c r="C307" t="n">
+        <v>320</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="n">
+        <v>12</v>
+      </c>
+      <c r="C308" t="n">
+        <v>280</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="n">
+        <v>12</v>
+      </c>
+      <c r="C309" t="n">
+        <v>300</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="n">
+        <v>12</v>
+      </c>
+      <c r="C310" t="n">
+        <v>320</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="n">
+        <v>14</v>
+      </c>
+      <c r="C311" t="n">
+        <v>280</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="n">
+        <v>14</v>
+      </c>
+      <c r="C312" t="n">
+        <v>300</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="n">
+        <v>14</v>
+      </c>
+      <c r="C313" t="n">
+        <v>320</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="n">
+        <v>16</v>
+      </c>
+      <c r="C314" t="n">
+        <v>280</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" t="n">
+        <v>16</v>
+      </c>
+      <c r="C315" t="n">
+        <v>300</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" t="n">
+        <v>16</v>
+      </c>
+      <c r="C316" t="n">
+        <v>320</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED</t>
         </is>
       </c>
     </row>
@@ -12934,13 +13310,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="C2" t="n">
-        <v>11.05050505050505</v>
+        <v>11.04761904761905</v>
       </c>
       <c r="D2" t="n">
-        <v>3.401233095273914</v>
+        <v>3.402081469593384</v>
       </c>
       <c r="E2" t="n">
         <v>6</v>
@@ -12971,13 +13347,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="C3" t="n">
-        <v>131.4646464646465</v>
+        <v>141.0952380952381</v>
       </c>
       <c r="D3" t="n">
-        <v>75.02900067207975</v>
+        <v>82.80794953332963</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -12986,19 +13362,19 @@
         <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H3" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="I3" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="J3" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="K3" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -13079,25 +13455,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7230498858542915</v>
+        <v>0.7286775900557158</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2350627733356611</v>
+        <v>0.2307185433910514</v>
       </c>
       <c r="E2" t="n">
         <v>0.026666667</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6184641131145288</v>
+        <v>0.6282685676692462</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8025718127012751</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.902382867756432</v>
+        <v>0.8997898151200044</v>
       </c>
       <c r="I2" t="n">
         <v>0.993333333</v>
@@ -13106,10 +13482,10 @@
         <v>0.9666666660000001</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.254047517839529</v>
+        <v>-1.311469159558903</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8249426887011246</v>
+        <v>1.021175028339839</v>
       </c>
     </row>
     <row r="3">
@@ -13119,37 +13495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="C3" t="n">
-        <v>2.522865379114382</v>
+        <v>2.573320218301397</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9167071588012904</v>
+        <v>0.9549443308150304</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.715322847090709</v>
+        <v>1.751300405422936</v>
       </c>
       <c r="G3" t="n">
-        <v>2.442990309873105</v>
+        <v>2.504700855</v>
       </c>
       <c r="H3" t="n">
-        <v>3.161149282</v>
+        <v>3.185185339195284</v>
       </c>
       <c r="I3" t="n">
-        <v>4.681919643</v>
+        <v>5.671841586375268</v>
       </c>
       <c r="J3" t="n">
-        <v>3.681919643</v>
+        <v>4.671841586375268</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4322597050479453</v>
+        <v>0.5139316261299347</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7817657152362756</v>
+        <v>-0.4833077489972979</v>
       </c>
     </row>
     <row r="4">
@@ -13159,25 +13535,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2029438288485386</v>
+        <v>0.2061559041596319</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08922722761139391</v>
+        <v>0.08916930388512323</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1461760839334437</v>
+        <v>0.1499340633601398</v>
       </c>
       <c r="G4" t="n">
-        <v>0.214618498</v>
+        <v>0.2192239410583238</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2747872074527885</v>
+        <v>0.2766218197776166</v>
       </c>
       <c r="I4" t="n">
         <v>0.367215621</v>
@@ -13186,10 +13562,10 @@
         <v>0.367215621</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.411751701194934</v>
+        <v>-0.4188078239746663</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6610897161462441</v>
+        <v>-0.6117398081313836</v>
       </c>
     </row>
   </sheetData>
@@ -13419,7 +13795,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01253657238082872</v>
+        <v>-0.01233811830356795</v>
       </c>
     </row>
     <row r="3">
@@ -13429,7 +13805,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.01253657238082872</v>
+        <v>-0.01233811830356795</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>

--- a/STEP2_ML/Step6_ML_Data_Preparation.xlsx
+++ b/STEP2_ML/Step6_ML_Data_Preparation.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-09 08:29:28</t>
+          <t>2026-10-12 10:41:57</t>
         </is>
       </c>
     </row>
